--- a/Collections/EURO/Bulgaria/#EURO#Bulgaria#Regular#[2026-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Bulgaria/#EURO#Bulgaria#Regular#[2026-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Bulgaria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC403392-CEDD-40B9-8997-2D7ADB4B5EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24443B21-5394-4565-88CD-8F7722CF10CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -787,6 +787,9 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -807,9 +810,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -817,14 +817,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="49">
+  <dxfs count="11">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -890,311 +891,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1226,9 +922,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="47" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1509,14 +1205,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
@@ -1526,7 +1222,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="25" t="s">
         <v>26</v>
       </c>
@@ -1551,7 +1247,7 @@
       <c r="B3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="11"/>
@@ -1572,7 +1268,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="45" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1608,14 +1304,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
@@ -1625,7 +1321,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="25" t="s">
         <v>26</v>
       </c>
@@ -1650,7 +1346,7 @@
       <c r="B3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="11"/>
@@ -1675,7 +1371,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1711,14 +1407,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
@@ -1728,7 +1424,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="25" t="s">
         <v>26</v>
       </c>
@@ -1753,7 +1449,7 @@
       <c r="B3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="11"/>
@@ -1778,7 +1474,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1814,14 +1510,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
@@ -1831,7 +1527,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="25" t="s">
         <v>26</v>
       </c>
@@ -1856,7 +1552,7 @@
       <c r="B3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="23" t="s">
@@ -1883,7 +1579,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1919,14 +1615,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
@@ -1936,7 +1632,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="25" t="s">
         <v>26</v>
       </c>
@@ -1961,7 +1657,7 @@
       <c r="B3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="23" t="s">
@@ -1988,7 +1684,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2024,14 +1720,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
@@ -2041,7 +1737,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="25" t="s">
         <v>26</v>
       </c>
@@ -2066,7 +1762,7 @@
       <c r="B3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="23" t="s">
@@ -2093,7 +1789,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2129,14 +1825,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
@@ -2146,7 +1842,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="25" t="s">
         <v>26</v>
       </c>
@@ -2171,7 +1867,7 @@
       <c r="B3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="23" t="s">
@@ -2202,7 +1898,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2238,14 +1934,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
@@ -2255,7 +1951,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="25" t="s">
         <v>26</v>
       </c>
@@ -2280,7 +1976,7 @@
       <c r="B3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="23" t="s">
@@ -2311,7 +2007,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
